--- a/mock-data/compliance-master-data.xlsx
+++ b/mock-data/compliance-master-data.xlsx
@@ -479,12 +479,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
@@ -551,12 +551,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>SKU-CHM-9100</t>
+          <t>SKU-FIN-9100</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>CHEMICAL</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>VOC limits in California</t>
+          <t>VOC limits in California (CARB)</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -598,12 +598,12 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>SKU-CHM-9100</t>
+          <t>SKU-FIN-9100</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>CHEMICAL</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Permitted with SDS</t>
+          <t>Permitted with SDS attached</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -646,7 +646,7 @@
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>CHEMICAL</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Import licence required - not held</t>
+          <t>Export licence required - not held</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>HSE</t>
+          <t>Customs</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SKU-PMP-7700</t>
+          <t>SKU-SHS-7700</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>PUMP</t>
+          <t>SHOWERSYS</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -747,7 +747,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -829,7 +829,7 @@
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Chemicals allowed with SDS attached</t>
+          <t>Finishes allowed with SDS attached</t>
         </is>
       </c>
     </row>
@@ -846,34 +846,34 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CHEMICAL</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>VOC-restricted chemicals require approval</t>
+          <t>VOC-restricted finishes require approval (CARB)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>CHEMICAL</t>
+          <t>FINISH</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Export licence required for chemicals</t>
+          <t>Export licence required for finishes</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>SKU-CHM-9100</t>
+          <t>SKU-FIN-9100</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>SDS-CHM-9100</t>
+          <t>SDS-FIN-9100</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>sds/SKU-CHM-9100_v4.2.pdf</t>
+          <t>sds/SKU-FIN-9100_v4.2.pdf</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>SKU-STL-4520</t>
+          <t>SKU-CTG-4520</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1072,7 +1072,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>SKU-FLG-3010</t>
+          <t>SKU-DRN-3010</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -1116,7 +1116,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SKU-PMP-7700</t>
+          <t>SKU-SHS-7700</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1138,7 +1138,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>SKU-GSK-1150</t>
+          <t>SKU-SEL-1150</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1160,7 +1160,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SKU-CHM-9100</t>
+          <t>SKU-FIN-9100</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1182,7 +1182,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>SKU-CHM-9100</t>
+          <t>SKU-FIN-9100</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1204,12 +1204,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>SKU-CHM-9100</t>
+          <t>SKU-FIN-9100</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">

--- a/mock-data/compliance-master-data.xlsx
+++ b/mock-data/compliance-master-data.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -487,6 +487,8 @@
     <col width="32" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -542,6 +544,16 @@
           <t>authority</t>
         </is>
       </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>eligible_flag</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>required_doc_type</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -589,6 +601,16 @@
           <t>EPA/CARB</t>
         </is>
       </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>SDS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -636,6 +658,16 @@
           <t>EPA</t>
         </is>
       </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>SDS</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -679,6 +711,16 @@
           <t>Customs</t>
         </is>
       </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Export Licence</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -726,10 +768,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mock-data/compliance-master-data.xlsx
+++ b/mock-data/compliance-master-data.xlsx
@@ -1057,7 +1057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1120,7 +1120,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>SKU-DRN-3010</t>
+          <t>SKU-CTG-1017</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -1142,7 +1142,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>SKU-VLV-2201</t>
+          <t>SKU-DRN-3010</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>SKU-SHS-7700</t>
+          <t>SKU-DRN-7213</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1186,7 +1186,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>SKU-SEL-1150</t>
+          <t>SKU-VLV-2201</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1208,12 +1208,12 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SKU-FIN-9100</t>
+          <t>SKU-SHS-7700</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1223,29 +1223,29 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>SDS must be attached</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>SKU-FIN-9100</t>
+          <t>SKU-SEL-1150</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Restricted - requires compliance approval</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1257,15 +1257,59 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>SDS must be attached</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>SKU-FIN-9100</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Restricted - requires compliance approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SKU-FIN-9100</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Export prohibited without licence</t>
         </is>
